--- a/Config/Datas/human_tech.xlsx
+++ b/Config/Datas/human_tech.xlsx
@@ -525,12 +525,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>???????</t>
+          <t>UI/Prefabs/TalentTreeLayouts/HumanTechTreeLayout</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>人类文明</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>????</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -736,10 +736,8 @@
           <t>????</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>??????</t>
-        </is>
+      <c r="F4" t="n">
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -768,7 +766,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>基础议事</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -800,7 +798,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>旧货估价</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -832,14 +830,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>酒馆识字</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -864,14 +862,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>简易木工</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -896,14 +894,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>地方安定</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -928,14 +926,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>工匠分工</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1058,7 +1056,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>EHumanCivilizationAttribute</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1127,7 +1125,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>??????????????</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1147,7 +1145,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>??key</t>
+          <t>??????</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1165,7 +1163,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>???????????</t>
+          <t>建立城镇管理的基本议事流程。</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1180,7 +1178,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>open_town_management</t>
+          <t>TownManagementAccess</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1196,7 +1194,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>?????????</t>
+          <t>允许将搜刮物交由城镇进行估价与贸易。</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1214,7 +1212,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>open_scavenge_exchange</t>
+          <t>ScavengeExchangeAccess</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1230,7 +1228,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>酒馆开始整理通识与秘闻，提升潜入准备。</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1248,7 +1246,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>tavern_human_knowledge</t>
+          <t>TavernHumanKnowledgeOutput</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1264,7 +1262,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>解锁基础木工加工与相关经营。</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1282,7 +1280,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>basic_woodworking</t>
+          <t>BasicWoodworkingAccess</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1298,7 +1296,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>???????????</t>
+          <t>城镇建设对周边安定产生稳定的正向影响。</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1316,7 +1314,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>town_stability</t>
+          <t>TownStabilityBonus</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1332,7 +1330,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>工匠分工提高二级材料加工建筑的效率。</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1350,7 +1348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>workshop_operation</t>
+          <t>WorkshopOperationEfficiency</t>
         </is>
       </c>
       <c r="I10" t="n">
